--- a/output/yearly_benthic_cover_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_93_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.25397279342594</v>
+        <v>45.16718912834529</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3740012564589</v>
+        <v>99.43754185813992</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05935765364828</v>
+        <v>88.0731413914159</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94342708313649</v>
+        <v>45.92727119747848</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228801622369725</v>
+        <v>2.228849202497459</v>
       </c>
       <c r="E3" t="n">
-        <v>5.716517995424306</v>
+        <v>5.708132389638205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429338741232419</v>
+        <v>0.7429497341658197</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97790684979931</v>
+        <v>33.97213608260869</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17495820966912</v>
+        <v>34.1756877716277</v>
       </c>
       <c r="I3" t="n">
-        <v>6.574902388992318</v>
+        <v>6.601950372341649</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643336713270261</v>
+        <v>4.643435838536373</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94064234635172</v>
+        <v>11.92685860858409</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8799328101727</v>
+        <v>48.90890663929428</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640022396609</v>
+        <v>106.7630364453568</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13418963068816</v>
+        <v>87.31414855750798</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6541732061165</v>
+        <v>42.81001212671637</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184194239515251</v>
+        <v>2.193089935320333</v>
       </c>
       <c r="E4" t="n">
-        <v>6.517206192175616</v>
+        <v>6.535419576846132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444943592151769</v>
+        <v>0.7445134494418149</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29787077829325</v>
+        <v>33.42709306695988</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24674052389813</v>
+        <v>34.24761867432348</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490593792495866</v>
+        <v>5.513204795605008</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653089745094856</v>
+        <v>4.653209059011343</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86581036931185</v>
+        <v>12.68585144249201</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29738024709965</v>
+        <v>44.32074892044878</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81736382252799</v>
+        <v>99.81661248965716</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.00872707366247</v>
+        <v>86.2959211538987</v>
       </c>
       <c r="C5" t="n">
-        <v>42.3808854833536</v>
+        <v>42.64761151323734</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129440033086391</v>
+        <v>2.143922690603083</v>
       </c>
       <c r="E5" t="n">
-        <v>7.117767541216264</v>
+        <v>7.15598511818814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458168921907143</v>
+        <v>0.7458370450154128</v>
       </c>
       <c r="G5" t="n">
-        <v>32.46314717301499</v>
+        <v>32.67768555815681</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30757704077286</v>
+        <v>34.30850407070898</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5836228171893</v>
+        <v>4.602505139879947</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661355576191964</v>
+        <v>4.661481531346331</v>
       </c>
       <c r="K5" t="n">
-        <v>13.99127292633753</v>
+        <v>13.7040788461013</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47532509607287</v>
+        <v>43.49516506300566</v>
       </c>
       <c r="M5" t="n">
-        <v>99.847483505764</v>
+        <v>99.84685542234429</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.70300863590194</v>
+        <v>85.06146419937453</v>
       </c>
       <c r="C6" t="n">
-        <v>41.78706748191301</v>
+        <v>42.12821028242261</v>
       </c>
       <c r="D6" t="n">
-        <v>2.065884520832419</v>
+        <v>2.084007502149422</v>
       </c>
       <c r="E6" t="n">
-        <v>7.542902491180584</v>
+        <v>7.596199247272017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469396680324446</v>
+        <v>0.7469597253447817</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49424834707967</v>
+        <v>31.76445781117322</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35922472949245</v>
+        <v>34.36014736585995</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825435954081604</v>
+        <v>3.84119426417025</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668372925202778</v>
+        <v>4.668498283404886</v>
       </c>
       <c r="K6" t="n">
-        <v>15.29699136409806</v>
+        <v>14.93853580062546</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78861829795591</v>
+        <v>42.80540655195527</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87267714396697</v>
+        <v>99.87215263500335</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.25646548380233</v>
+        <v>83.64715677792877</v>
       </c>
       <c r="C7" t="n">
-        <v>40.9347424242035</v>
+        <v>41.31081606785065</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995726835699452</v>
+        <v>2.015461242606832</v>
       </c>
       <c r="E7" t="n">
-        <v>7.818734160909187</v>
+        <v>7.880528998711421</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478942223428899</v>
+        <v>0.7479137599120346</v>
       </c>
       <c r="G7" t="n">
-        <v>30.42469991068227</v>
+        <v>30.71967521460931</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40313422777293</v>
+        <v>34.40403295595358</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191937236752522</v>
+        <v>3.205083606685362</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674338889643061</v>
+        <v>4.674460999450216</v>
       </c>
       <c r="K7" t="n">
-        <v>16.74353451619768</v>
+        <v>16.35284322207123</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21546094976323</v>
+        <v>42.22964086940672</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8937378901644</v>
+        <v>99.8933001593286</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.0377932041656</v>
+        <v>88.51533854723174</v>
       </c>
       <c r="C8" t="n">
-        <v>43.16754454846972</v>
+        <v>43.618733060328</v>
       </c>
       <c r="D8" t="n">
-        <v>1.999971855722515</v>
+        <v>2.019743749656226</v>
       </c>
       <c r="E8" t="n">
-        <v>9.604218655650122</v>
+        <v>9.717370544550723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494850342176353</v>
+        <v>0.7495029474793529</v>
       </c>
       <c r="G8" t="n">
-        <v>30.90568872874413</v>
+        <v>31.22479809298547</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47631157401122</v>
+        <v>34.47713558405022</v>
       </c>
       <c r="I8" t="n">
-        <v>5.617835891959762</v>
+        <v>5.642394206763775</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68428146386022</v>
+        <v>4.684393421745955</v>
       </c>
       <c r="K8" t="n">
-        <v>11.96220679583439</v>
+        <v>11.48466145276828</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68338492865461</v>
+        <v>44.70892446975856</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81313627295873</v>
+        <v>99.81231898285483</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.05766791380842</v>
+        <v>86.67220306269009</v>
       </c>
       <c r="C9" t="n">
-        <v>42.05949396897162</v>
+        <v>42.65194571218068</v>
       </c>
       <c r="D9" t="n">
-        <v>1.910276418106807</v>
+        <v>1.936595509289122</v>
       </c>
       <c r="E9" t="n">
-        <v>9.955157712126514</v>
+        <v>10.10241414483652</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508465672250836</v>
+        <v>0.7508607621550188</v>
       </c>
       <c r="G9" t="n">
-        <v>29.51961958611708</v>
+        <v>29.93934442209688</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53894209235384</v>
+        <v>34.53959505913085</v>
       </c>
       <c r="I9" t="n">
-        <v>4.690034492722318</v>
+        <v>4.71051340171283</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692791045156771</v>
+        <v>4.692879763468866</v>
       </c>
       <c r="K9" t="n">
-        <v>13.94233208619158</v>
+        <v>13.3277969373099</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84212294783791</v>
+        <v>43.86352417809933</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84394900300111</v>
+        <v>99.8432668275899</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.90836752609587</v>
+        <v>84.60282477392401</v>
       </c>
       <c r="C10" t="n">
-        <v>40.63799357540772</v>
+        <v>41.31407452207158</v>
       </c>
       <c r="D10" t="n">
-        <v>1.813883999411613</v>
+        <v>1.843980400314868</v>
       </c>
       <c r="E10" t="n">
-        <v>10.10522775445165</v>
+        <v>10.27453099250799</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520141677642249</v>
+        <v>0.7520238499363991</v>
       </c>
       <c r="G10" t="n">
-        <v>28.03006158084795</v>
+        <v>28.50753502619053</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59265171715434</v>
+        <v>34.59309709707435</v>
       </c>
       <c r="I10" t="n">
-        <v>3.914439757939688</v>
+        <v>3.931508345797381</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700088548526405</v>
+        <v>4.700149062102494</v>
       </c>
       <c r="K10" t="n">
-        <v>16.09163247390412</v>
+        <v>15.39717522607598</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14009521477921</v>
+        <v>43.15790265736041</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86972126409105</v>
+        <v>99.86915240550796</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.65859128102426</v>
+        <v>82.30412452193647</v>
       </c>
       <c r="C11" t="n">
-        <v>38.99508344600655</v>
+        <v>39.62541284276745</v>
       </c>
       <c r="D11" t="n">
-        <v>1.714015710037556</v>
+        <v>1.741955808853132</v>
       </c>
       <c r="E11" t="n">
-        <v>10.09325420356704</v>
+        <v>10.25282536728474</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530168652655442</v>
+        <v>0.7530230290785936</v>
       </c>
       <c r="G11" t="n">
-        <v>26.48679073109307</v>
+        <v>26.93025708216705</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63877580221503</v>
+        <v>34.63905933761529</v>
       </c>
       <c r="I11" t="n">
-        <v>3.266382560936358</v>
+        <v>3.280609965196465</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70635540790965</v>
+        <v>4.706393931741209</v>
       </c>
       <c r="K11" t="n">
-        <v>18.34140871897575</v>
+        <v>17.69587547806351</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55477339729715</v>
+        <v>42.56950311400799</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89126556227944</v>
+        <v>99.89079143483896</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.28840455939998</v>
+        <v>80.03600663724444</v>
       </c>
       <c r="C12" t="n">
-        <v>37.13055503291343</v>
+        <v>37.86558367563542</v>
       </c>
       <c r="D12" t="n">
-        <v>1.609769912347306</v>
+        <v>1.642323947879566</v>
       </c>
       <c r="E12" t="n">
-        <v>9.933570223883251</v>
+        <v>10.12257056019441</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538795593825668</v>
+        <v>0.7538813895504223</v>
       </c>
       <c r="G12" t="n">
-        <v>24.87587397470171</v>
+        <v>25.38997022990795</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67845973159807</v>
+        <v>34.67854391931941</v>
       </c>
       <c r="I12" t="n">
-        <v>2.725103911346039</v>
+        <v>2.736957905702537</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711747246141041</v>
+        <v>4.711758684690138</v>
       </c>
       <c r="K12" t="n">
-        <v>20.71159544060002</v>
+        <v>19.96399336275557</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06711667757164</v>
+        <v>42.07929490702023</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90926715108509</v>
+        <v>99.90887194541122</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.84425592384838</v>
+        <v>77.66614924357731</v>
       </c>
       <c r="C13" t="n">
-        <v>35.10743168911685</v>
+        <v>35.9190217763239</v>
       </c>
       <c r="D13" t="n">
-        <v>1.503216595271502</v>
+        <v>1.539077804601494</v>
       </c>
       <c r="E13" t="n">
-        <v>9.65491073886926</v>
+        <v>9.866711750731454</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546229193138874</v>
+        <v>0.7546200795190168</v>
       </c>
       <c r="G13" t="n">
-        <v>23.22929897858993</v>
+        <v>23.79380736108562</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71265428843881</v>
+        <v>34.71252365787476</v>
       </c>
       <c r="I13" t="n">
-        <v>2.273159157653191</v>
+        <v>2.2830330927711</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716393245711794</v>
+        <v>4.716375496993854</v>
       </c>
       <c r="K13" t="n">
-        <v>23.15574407615163</v>
+        <v>22.33385075642271</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6611269038608</v>
+        <v>41.67110085876166</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92430266912928</v>
+        <v>99.92397339150827</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.58815308053721</v>
+        <v>84.15568179340818</v>
       </c>
       <c r="C14" t="n">
-        <v>39.33392251521008</v>
+        <v>39.92016518480592</v>
       </c>
       <c r="D14" t="n">
-        <v>1.504940735371565</v>
+        <v>1.540891873192875</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00400738741059</v>
+        <v>12.11163270030405</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554884470360455</v>
+        <v>0.7555095294094565</v>
       </c>
       <c r="G14" t="n">
-        <v>25.11460066359987</v>
+        <v>25.55918388040524</v>
       </c>
       <c r="H14" t="n">
-        <v>36.61112700511195</v>
+        <v>36.49076976717417</v>
       </c>
       <c r="I14" t="n">
-        <v>2.876186048031911</v>
+        <v>2.975759484113302</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721802793975282</v>
+        <v>4.721934558809103</v>
       </c>
       <c r="K14" t="n">
-        <v>16.4118469194628</v>
+        <v>15.84431820659181</v>
       </c>
       <c r="L14" t="n">
-        <v>44.15846753411331</v>
+        <v>44.13644140301282</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90423696878618</v>
+        <v>99.90092479441056</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.77856465370711</v>
+        <v>83.47424089441344</v>
       </c>
       <c r="C15" t="n">
-        <v>38.96891909103685</v>
+        <v>39.69907701266594</v>
       </c>
       <c r="D15" t="n">
-        <v>1.474819091457563</v>
+        <v>1.515614305127856</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16360135204604</v>
+        <v>12.3266569664401</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562183141128854</v>
+        <v>0.7562584108456141</v>
       </c>
       <c r="G15" t="n">
-        <v>24.61192767425817</v>
+        <v>25.13989812683413</v>
       </c>
       <c r="H15" t="n">
-        <v>36.64649651519761</v>
+        <v>36.52694040302452</v>
       </c>
       <c r="I15" t="n">
-        <v>2.399137243429305</v>
+        <v>2.482257614356133</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726364463205532</v>
+        <v>4.726615067785088</v>
       </c>
       <c r="K15" t="n">
-        <v>17.22143534629289</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="L15" t="n">
-        <v>43.7297515057805</v>
+        <v>43.6925038960777</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92010594311024</v>
+        <v>99.91734001433019</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.29996585974929</v>
+        <v>81.13970375857679</v>
       </c>
       <c r="C16" t="n">
-        <v>36.86118114394867</v>
+        <v>37.74864867540494</v>
       </c>
       <c r="D16" t="n">
-        <v>1.380397352613053</v>
+        <v>1.426060096052253</v>
       </c>
       <c r="E16" t="n">
-        <v>11.71834635985215</v>
+        <v>11.94335400854442</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568464375554933</v>
+        <v>0.7569016172592058</v>
       </c>
       <c r="G16" t="n">
-        <v>23.03620830584258</v>
+        <v>23.654438610272</v>
       </c>
       <c r="H16" t="n">
-        <v>36.67693550764339</v>
+        <v>36.55800698291199</v>
       </c>
       <c r="I16" t="n">
-        <v>2.00094166152078</v>
+        <v>2.070307335666872</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730290234721831</v>
+        <v>4.730635107870036</v>
       </c>
       <c r="K16" t="n">
-        <v>19.70003414025073</v>
+        <v>18.86029624142322</v>
       </c>
       <c r="L16" t="n">
-        <v>43.37214201459423</v>
+        <v>43.32210348277305</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93335729879362</v>
+        <v>99.93104839960122</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.97675166869466</v>
+        <v>82.69302497623607</v>
       </c>
       <c r="C17" t="n">
-        <v>38.08861741698448</v>
+        <v>38.89508402799949</v>
       </c>
       <c r="D17" t="n">
-        <v>1.381510501832359</v>
+        <v>1.427242303247487</v>
       </c>
       <c r="E17" t="n">
-        <v>12.49195269912404</v>
+        <v>12.68226359981902</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574567567650342</v>
+        <v>0.7575290904915648</v>
       </c>
       <c r="G17" t="n">
-        <v>23.48841203189092</v>
+        <v>24.06029315116863</v>
       </c>
       <c r="H17" t="n">
-        <v>37.14013908442797</v>
+        <v>36.97455861253339</v>
       </c>
       <c r="I17" t="n">
-        <v>1.983175864872877</v>
+        <v>2.056581403403708</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734104729781462</v>
+        <v>4.734556815572279</v>
       </c>
       <c r="K17" t="n">
-        <v>18.02324833130535</v>
+        <v>17.30697502376392</v>
       </c>
       <c r="L17" t="n">
-        <v>43.82208165420897</v>
+        <v>43.72944501807805</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9339474024988</v>
+        <v>99.93150406984145</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.59859548235831</v>
+        <v>80.44701203089134</v>
       </c>
       <c r="C18" t="n">
-        <v>36.01661689561946</v>
+        <v>36.96695150541028</v>
       </c>
       <c r="D18" t="n">
-        <v>1.294470536506502</v>
+        <v>1.344214110458263</v>
       </c>
       <c r="E18" t="n">
-        <v>11.98054809309294</v>
+        <v>12.23032666989955</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579813368939795</v>
+        <v>0.7580674114799251</v>
       </c>
       <c r="G18" t="n">
-        <v>22.00856040129991</v>
+        <v>22.66061304515227</v>
       </c>
       <c r="H18" t="n">
-        <v>37.16586065701406</v>
+        <v>37.0008337499325</v>
       </c>
       <c r="I18" t="n">
-        <v>1.653791101963548</v>
+        <v>1.715035722219305</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737383355587371</v>
+        <v>4.737921321749531</v>
       </c>
       <c r="K18" t="n">
-        <v>20.40140451764169</v>
+        <v>19.55298796910864</v>
       </c>
       <c r="L18" t="n">
-        <v>43.52689036827017</v>
+        <v>43.42293326427543</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94491178153132</v>
+        <v>99.94287273879435</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.58381196786362</v>
+        <v>79.5458658131632</v>
       </c>
       <c r="C19" t="n">
-        <v>35.25647006190466</v>
+        <v>36.33027442512566</v>
       </c>
       <c r="D19" t="n">
-        <v>1.257975934080265</v>
+        <v>1.3115698207052</v>
       </c>
       <c r="E19" t="n">
-        <v>11.87261181438306</v>
+        <v>12.17165487962654</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584246979323201</v>
+        <v>0.758521688804739</v>
       </c>
       <c r="G19" t="n">
-        <v>21.38807995066957</v>
+        <v>22.1102992130978</v>
       </c>
       <c r="H19" t="n">
-        <v>37.18759983945784</v>
+        <v>37.02300676451835</v>
       </c>
       <c r="I19" t="n">
-        <v>1.37896536926355</v>
+        <v>1.430052891380945</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740154362077</v>
+        <v>4.740760555029619</v>
       </c>
       <c r="K19" t="n">
-        <v>21.41618803213641</v>
+        <v>20.45413418683679</v>
       </c>
       <c r="L19" t="n">
-        <v>43.28140326423772</v>
+        <v>43.16795150686478</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95406135827878</v>
+        <v>99.95236011882724</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.02367902706807</v>
+        <v>77.05344401152958</v>
       </c>
       <c r="C20" t="n">
-        <v>32.90848242422295</v>
+        <v>34.05824225773689</v>
       </c>
       <c r="D20" t="n">
-        <v>1.165263228733388</v>
+        <v>1.22035682183732</v>
       </c>
       <c r="E20" t="n">
-        <v>11.18922098120122</v>
+        <v>11.52389919924912</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588070234790455</v>
+        <v>0.7589129344345013</v>
       </c>
       <c r="G20" t="n">
-        <v>19.81178051545688</v>
+        <v>20.57264054997879</v>
       </c>
       <c r="H20" t="n">
-        <v>37.20634628782481</v>
+        <v>37.04210323837146</v>
       </c>
       <c r="I20" t="n">
-        <v>1.14971709362869</v>
+        <v>1.192325427442758</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742543896744033</v>
+        <v>4.743205840215633</v>
       </c>
       <c r="K20" t="n">
-        <v>23.97632097293194</v>
+        <v>22.94655598847042</v>
       </c>
       <c r="L20" t="n">
-        <v>43.07689200925446</v>
+        <v>42.95547806236542</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96169540640936</v>
+        <v>99.96027630857273</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.98355518028509</v>
+        <v>82.59865938690388</v>
       </c>
       <c r="C21" t="n">
-        <v>36.63097137594395</v>
+        <v>37.45581232243262</v>
       </c>
       <c r="D21" t="n">
-        <v>1.166037121566148</v>
+        <v>1.22122189351175</v>
       </c>
       <c r="E21" t="n">
-        <v>13.18695306601979</v>
+        <v>13.36964634468141</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593109742623864</v>
+        <v>0.7594509033884911</v>
       </c>
       <c r="G21" t="n">
-        <v>21.54299814748086</v>
+        <v>22.13204440070988</v>
       </c>
       <c r="H21" t="n">
-        <v>38.94911627080973</v>
+        <v>38.61318176114098</v>
       </c>
       <c r="I21" t="n">
-        <v>1.633446011006251</v>
+        <v>1.756545937293307</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745693589139914</v>
+        <v>4.74656814617807</v>
       </c>
       <c r="K21" t="n">
-        <v>18.01644481971492</v>
+        <v>17.40134061309612</v>
       </c>
       <c r="L21" t="n">
-        <v>45.29817174096445</v>
+        <v>45.08433700912327</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94558793662331</v>
+        <v>99.94148994465201</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_93_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.16718912834529</v>
+        <v>45.17383575291625</v>
       </c>
       <c r="M2" t="n">
-        <v>99.43754185813992</v>
+        <v>101.0720056753344</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0731413914159</v>
+        <v>88.01808498016175</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92727119747848</v>
+        <v>45.91639718264624</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228849202497459</v>
+        <v>2.228716270950023</v>
       </c>
       <c r="E3" t="n">
-        <v>5.708132389638205</v>
+        <v>5.698854108738175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429497341658197</v>
+        <v>0.7429054236500079</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97213608260869</v>
+        <v>33.96894982348158</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1756877716277</v>
+        <v>34.17364948790036</v>
       </c>
       <c r="I3" t="n">
-        <v>6.601950372341649</v>
+        <v>6.561850967629052</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643435838536373</v>
+        <v>4.643158897812548</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92685860858409</v>
+        <v>11.98191501983825</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90890663929428</v>
+        <v>48.86614948146661</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630364453568</v>
+        <v>106.7644616839511</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.31414855750798</v>
+        <v>87.16052588199169</v>
       </c>
       <c r="C4" t="n">
-        <v>42.81001212671637</v>
+        <v>42.69323471859821</v>
       </c>
       <c r="D4" t="n">
-        <v>2.193089935320333</v>
+        <v>2.18767273290922</v>
       </c>
       <c r="E4" t="n">
-        <v>6.535419576846132</v>
+        <v>6.507183366251505</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445134494418149</v>
+        <v>0.7444622734458751</v>
       </c>
       <c r="G4" t="n">
-        <v>33.42709306695988</v>
+        <v>33.34338527654538</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24761867432348</v>
+        <v>34.24526457851024</v>
       </c>
       <c r="I4" t="n">
-        <v>5.513204795605008</v>
+        <v>5.47966844529274</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653209059011343</v>
+        <v>4.652889209036719</v>
       </c>
       <c r="K4" t="n">
-        <v>12.68585144249201</v>
+        <v>12.83947411800831</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32074892044878</v>
+        <v>44.28501752540378</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81661248965716</v>
+        <v>99.8177263620103</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.2959211538987</v>
+        <v>85.95670575231514</v>
       </c>
       <c r="C5" t="n">
-        <v>42.64761151323734</v>
+        <v>42.33994858132162</v>
       </c>
       <c r="D5" t="n">
-        <v>2.143922690603083</v>
+        <v>2.128795550326046</v>
       </c>
       <c r="E5" t="n">
-        <v>7.15598511818814</v>
+        <v>7.094469664575099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458370450154128</v>
+        <v>0.7457829134452268</v>
       </c>
       <c r="G5" t="n">
-        <v>32.67768555815681</v>
+        <v>32.44600947012957</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30850407070898</v>
+        <v>34.30601401848043</v>
       </c>
       <c r="I5" t="n">
-        <v>4.602505139879947</v>
+        <v>4.574490926326088</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661481531346331</v>
+        <v>4.661143209032667</v>
       </c>
       <c r="K5" t="n">
-        <v>13.7040788461013</v>
+        <v>14.04329424768488</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49516506300566</v>
+        <v>43.46454415862425</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84685542234429</v>
+        <v>99.84778698763076</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.06146419937453</v>
+        <v>84.66942546895639</v>
       </c>
       <c r="C6" t="n">
-        <v>42.12821028242261</v>
+        <v>41.76312327710696</v>
       </c>
       <c r="D6" t="n">
-        <v>2.084007502149422</v>
+        <v>2.066131895058216</v>
       </c>
       <c r="E6" t="n">
-        <v>7.596199247272017</v>
+        <v>7.521936326572789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469597253447817</v>
+        <v>0.7469038430796655</v>
       </c>
       <c r="G6" t="n">
-        <v>31.76445781117322</v>
+        <v>31.49092218993419</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36014736585995</v>
+        <v>34.3575767816646</v>
       </c>
       <c r="I6" t="n">
-        <v>3.84119426417025</v>
+        <v>3.817805413399018</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668498283404886</v>
+        <v>4.668149019247909</v>
       </c>
       <c r="K6" t="n">
-        <v>14.93853580062546</v>
+        <v>15.33057453104361</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80540655195527</v>
+        <v>42.7792329994515</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87215263500335</v>
+        <v>99.87293080760206</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.64715677792877</v>
+        <v>83.31261373372995</v>
       </c>
       <c r="C7" t="n">
-        <v>41.31081606785065</v>
+        <v>40.99933327127939</v>
       </c>
       <c r="D7" t="n">
-        <v>2.015461242606832</v>
+        <v>2.000435323293757</v>
       </c>
       <c r="E7" t="n">
-        <v>7.880528998711421</v>
+        <v>7.813688711078889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479137599120346</v>
+        <v>0.747855802413893</v>
       </c>
       <c r="G7" t="n">
-        <v>30.71967521460931</v>
+        <v>30.48960875271932</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40403295595358</v>
+        <v>34.40136691103907</v>
       </c>
       <c r="I7" t="n">
-        <v>3.205083606685362</v>
+        <v>3.185559468098194</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674460999450216</v>
+        <v>4.674098765086831</v>
       </c>
       <c r="K7" t="n">
-        <v>16.35284322207123</v>
+        <v>16.68738626627005</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22964086940672</v>
+        <v>42.20723031207836</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8933001593286</v>
+        <v>99.8939498496278</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.51533854723174</v>
+        <v>88.40774132933721</v>
       </c>
       <c r="C8" t="n">
-        <v>43.618733060328</v>
+        <v>43.3733409289997</v>
       </c>
       <c r="D8" t="n">
-        <v>2.019743749656226</v>
+        <v>2.004794319209144</v>
       </c>
       <c r="E8" t="n">
-        <v>9.717370544550723</v>
+        <v>9.70299352019908</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495029474793529</v>
+        <v>0.7494853979074645</v>
       </c>
       <c r="G8" t="n">
-        <v>31.22479809298547</v>
+        <v>31.01057922812044</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47713558405022</v>
+        <v>34.47632830374336</v>
       </c>
       <c r="I8" t="n">
-        <v>5.642394206763775</v>
+        <v>5.77927682323608</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684393421745955</v>
+        <v>4.684283736921652</v>
       </c>
       <c r="K8" t="n">
-        <v>11.48466145276828</v>
+        <v>11.59225867066281</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70892446975856</v>
+        <v>44.84217669955648</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81231898285483</v>
+        <v>99.80777629921897</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.67220306269009</v>
+        <v>86.74018868278242</v>
       </c>
       <c r="C9" t="n">
-        <v>42.65194571218068</v>
+        <v>42.60297715544191</v>
       </c>
       <c r="D9" t="n">
-        <v>1.936595509289122</v>
+        <v>1.930107409926679</v>
       </c>
       <c r="E9" t="n">
-        <v>10.10241414483652</v>
+        <v>10.1456823953349</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508607621550188</v>
+        <v>0.7508750891816629</v>
       </c>
       <c r="G9" t="n">
-        <v>29.93934442209688</v>
+        <v>29.85530644257056</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53959505913085</v>
+        <v>34.54025410235649</v>
       </c>
       <c r="I9" t="n">
-        <v>4.71051340171283</v>
+        <v>4.824993936026722</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692879763468866</v>
+        <v>4.692969307385392</v>
       </c>
       <c r="K9" t="n">
-        <v>13.3277969373099</v>
+        <v>13.2598113172176</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86352417809933</v>
+        <v>43.97667606002841</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8432668275899</v>
+        <v>99.83946453268791</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.60282477392401</v>
+        <v>84.85239135299349</v>
       </c>
       <c r="C10" t="n">
-        <v>41.31407452207158</v>
+        <v>41.46431205389531</v>
       </c>
       <c r="D10" t="n">
-        <v>1.843980400314868</v>
+        <v>1.846127270084362</v>
       </c>
       <c r="E10" t="n">
-        <v>10.27453099250799</v>
+        <v>10.37543585293663</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520238499363991</v>
+        <v>0.7520630015617464</v>
       </c>
       <c r="G10" t="n">
-        <v>28.50753502619053</v>
+        <v>28.5562840165712</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59309709707435</v>
+        <v>34.59489807184033</v>
       </c>
       <c r="I10" t="n">
-        <v>3.931508345797381</v>
+        <v>4.02718938023833</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700149062102494</v>
+        <v>4.700393759760915</v>
       </c>
       <c r="K10" t="n">
-        <v>15.39717522607598</v>
+        <v>15.14760864700648</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15790265736041</v>
+        <v>43.25405168976415</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86915240550796</v>
+        <v>99.86597239066595</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.30412452193647</v>
+        <v>82.66635567501547</v>
       </c>
       <c r="C11" t="n">
-        <v>39.62541284276745</v>
+        <v>39.90320632154231</v>
       </c>
       <c r="D11" t="n">
-        <v>1.741955808853132</v>
+        <v>1.74952682412098</v>
       </c>
       <c r="E11" t="n">
-        <v>10.25282536728474</v>
+        <v>10.39262063745925</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530230290785936</v>
+        <v>0.753082092830609</v>
       </c>
       <c r="G11" t="n">
-        <v>26.93025708216705</v>
+        <v>27.06204804716714</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63905933761529</v>
+        <v>34.64177627020801</v>
       </c>
       <c r="I11" t="n">
-        <v>3.280609965196465</v>
+        <v>3.360538723038178</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706393931741209</v>
+        <v>4.706763080191306</v>
       </c>
       <c r="K11" t="n">
-        <v>17.69587547806351</v>
+        <v>17.33364432498453</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56950311400799</v>
+        <v>42.65128298179985</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89079143483896</v>
+        <v>99.8881336283267</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.03600663724444</v>
+        <v>80.44808527672264</v>
       </c>
       <c r="C12" t="n">
-        <v>37.86558367563542</v>
+        <v>38.205748692596</v>
       </c>
       <c r="D12" t="n">
-        <v>1.642323947879566</v>
+        <v>1.65245169672129</v>
       </c>
       <c r="E12" t="n">
-        <v>10.12257056019441</v>
+        <v>10.28325415331505</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538813895504223</v>
+        <v>0.7539569501714365</v>
       </c>
       <c r="G12" t="n">
-        <v>25.38997022990795</v>
+        <v>25.56046960569616</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67854391931941</v>
+        <v>34.68201970788607</v>
       </c>
       <c r="I12" t="n">
-        <v>2.736957905702537</v>
+        <v>2.803702224361154</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711758684690138</v>
+        <v>4.712230938571477</v>
       </c>
       <c r="K12" t="n">
-        <v>19.96399336275557</v>
+        <v>19.55191472327736</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07929490702023</v>
+        <v>42.14898828626446</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90887194541122</v>
+        <v>99.90665170213784</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.66614924357731</v>
+        <v>78.18087998913063</v>
       </c>
       <c r="C13" t="n">
-        <v>35.9190217763239</v>
+        <v>36.37233020502873</v>
       </c>
       <c r="D13" t="n">
-        <v>1.539077804601494</v>
+        <v>1.554084362968663</v>
       </c>
       <c r="E13" t="n">
-        <v>9.866711750731454</v>
+        <v>10.06090280404872</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546200795190168</v>
+        <v>0.7547087603861784</v>
       </c>
       <c r="G13" t="n">
-        <v>23.79380736108562</v>
+        <v>24.03890304519325</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71252365787476</v>
+        <v>34.7166029777642</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2830330927711</v>
+        <v>2.338748286356007</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716375496993854</v>
+        <v>4.716929752413614</v>
       </c>
       <c r="K13" t="n">
-        <v>22.33385075642271</v>
+        <v>21.81912001086939</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67110085876166</v>
+        <v>41.73066916675851</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92397339150827</v>
+        <v>99.92211938265662</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.15568179340818</v>
+        <v>84.4668172758381</v>
       </c>
       <c r="C14" t="n">
-        <v>39.92016518480592</v>
+        <v>40.21437547391154</v>
       </c>
       <c r="D14" t="n">
-        <v>1.540891873192875</v>
+        <v>1.555969142733141</v>
       </c>
       <c r="E14" t="n">
-        <v>12.11163270030405</v>
+        <v>12.23440215615978</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555095294094565</v>
+        <v>0.7556240644929215</v>
       </c>
       <c r="G14" t="n">
-        <v>25.55918388040524</v>
+        <v>25.71715174927353</v>
       </c>
       <c r="H14" t="n">
-        <v>36.49076976717417</v>
+        <v>36.40780150184372</v>
       </c>
       <c r="I14" t="n">
-        <v>2.975759484113302</v>
+        <v>3.073218258254244</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721934558809103</v>
+        <v>4.722650403080759</v>
       </c>
       <c r="K14" t="n">
-        <v>15.84431820659181</v>
+        <v>15.53318272416191</v>
       </c>
       <c r="L14" t="n">
-        <v>44.13644140301282</v>
+        <v>44.15012528188827</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90092479441056</v>
+        <v>99.89768347996171</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.47424089441344</v>
+        <v>83.82871072050881</v>
       </c>
       <c r="C15" t="n">
-        <v>39.69907701266594</v>
+        <v>40.05187642653205</v>
       </c>
       <c r="D15" t="n">
-        <v>1.515614305127856</v>
+        <v>1.532398397421157</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3266569664401</v>
+        <v>12.47633914285089</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562584108456141</v>
+        <v>0.7563943405308684</v>
       </c>
       <c r="G15" t="n">
-        <v>25.13989812683413</v>
+        <v>25.32757305045241</v>
       </c>
       <c r="H15" t="n">
-        <v>36.52694040302452</v>
+        <v>36.44491527099031</v>
       </c>
       <c r="I15" t="n">
-        <v>2.482257614356133</v>
+        <v>2.563625889945236</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726615067785088</v>
+        <v>4.727464628317927</v>
       </c>
       <c r="K15" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17128927949121</v>
       </c>
       <c r="L15" t="n">
-        <v>43.6925038960777</v>
+        <v>43.69146712013634</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91734001433019</v>
+        <v>99.9146328261596</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.13970375857679</v>
+        <v>81.47403793925804</v>
       </c>
       <c r="C16" t="n">
-        <v>37.74864867540494</v>
+        <v>38.09409130138584</v>
       </c>
       <c r="D16" t="n">
-        <v>1.426060096052253</v>
+        <v>1.441929289979149</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94335400854442</v>
+        <v>12.09613678956673</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569016172592058</v>
+        <v>0.757056040228219</v>
       </c>
       <c r="G16" t="n">
-        <v>23.654438610272</v>
+        <v>23.83229419124533</v>
       </c>
       <c r="H16" t="n">
-        <v>36.55800698291199</v>
+        <v>36.47679756850705</v>
       </c>
       <c r="I16" t="n">
-        <v>2.070307335666872</v>
+        <v>2.138223808305187</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730635107870036</v>
+        <v>4.731600251426369</v>
       </c>
       <c r="K16" t="n">
-        <v>18.86029624142322</v>
+        <v>18.52596206074197</v>
       </c>
       <c r="L16" t="n">
-        <v>43.32210348277305</v>
+        <v>43.30873480759593</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93104839960122</v>
+        <v>99.92878816972375</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.69302497623607</v>
+        <v>83.07708467813741</v>
       </c>
       <c r="C17" t="n">
-        <v>38.89508402799949</v>
+        <v>39.2600800294982</v>
       </c>
       <c r="D17" t="n">
-        <v>1.427242303247487</v>
+        <v>1.443174110777974</v>
       </c>
       <c r="E17" t="n">
-        <v>12.68226359981902</v>
+        <v>12.8527017715588</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575290904915648</v>
+        <v>0.7577096084103079</v>
       </c>
       <c r="G17" t="n">
-        <v>24.06029315116863</v>
+        <v>24.24038785413343</v>
       </c>
       <c r="H17" t="n">
-        <v>36.97455861253339</v>
+        <v>36.89580725959723</v>
       </c>
       <c r="I17" t="n">
-        <v>2.056581403403708</v>
+        <v>2.151619021095261</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734556815572279</v>
+        <v>4.735685052564424</v>
       </c>
       <c r="K17" t="n">
-        <v>17.30697502376392</v>
+        <v>16.92291532186256</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72944501807805</v>
+        <v>43.74534587778077</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93150406984145</v>
+        <v>99.92834122914154</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.44701203089134</v>
+        <v>80.77398310379077</v>
       </c>
       <c r="C18" t="n">
-        <v>36.96695150541028</v>
+        <v>37.28970774568594</v>
       </c>
       <c r="D18" t="n">
-        <v>1.344214110458263</v>
+        <v>1.357928266248554</v>
       </c>
       <c r="E18" t="n">
-        <v>12.23032666989955</v>
+        <v>12.39257175595632</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580674114799251</v>
+        <v>0.7582706765868665</v>
       </c>
       <c r="G18" t="n">
-        <v>22.66061304515227</v>
+        <v>22.80854929847061</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0008337499325</v>
+        <v>36.92312783607142</v>
       </c>
       <c r="I18" t="n">
-        <v>1.715035722219305</v>
+        <v>1.794343541789072</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737921321749531</v>
+        <v>4.739191728667915</v>
       </c>
       <c r="K18" t="n">
-        <v>19.55298796910864</v>
+        <v>19.22601689620924</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42293326427543</v>
+        <v>43.42450816307438</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94287273879435</v>
+        <v>99.94023280496957</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.5458658131632</v>
+        <v>79.84656531749695</v>
       </c>
       <c r="C19" t="n">
-        <v>36.33027442512566</v>
+        <v>36.63911659177258</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3115698207052</v>
+        <v>1.324307470957961</v>
       </c>
       <c r="E19" t="n">
-        <v>12.17165487962654</v>
+        <v>12.33511549259036</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758521688804739</v>
+        <v>0.7587443099677023</v>
       </c>
       <c r="G19" t="n">
-        <v>22.1102992130978</v>
+        <v>22.24383495685241</v>
       </c>
       <c r="H19" t="n">
-        <v>37.02300676451835</v>
+        <v>36.94619087465119</v>
       </c>
       <c r="I19" t="n">
-        <v>1.430052891380945</v>
+        <v>1.496220275179209</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740760555029619</v>
+        <v>4.742151937298138</v>
       </c>
       <c r="K19" t="n">
-        <v>20.45413418683679</v>
+        <v>20.15343468250303</v>
       </c>
       <c r="L19" t="n">
-        <v>43.16795150686478</v>
+        <v>43.15760584956357</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95236011882724</v>
+        <v>99.95015712383919</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.05344401152958</v>
+        <v>77.39939226755206</v>
       </c>
       <c r="C20" t="n">
-        <v>34.05824225773689</v>
+        <v>34.4226375519762</v>
       </c>
       <c r="D20" t="n">
-        <v>1.22035682183732</v>
+        <v>1.23470542401387</v>
       </c>
       <c r="E20" t="n">
-        <v>11.52389919924912</v>
+        <v>11.70844715454585</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589129344345013</v>
+        <v>0.7591519569202345</v>
       </c>
       <c r="G20" t="n">
-        <v>20.57264054997879</v>
+        <v>20.7388271035185</v>
       </c>
       <c r="H20" t="n">
-        <v>37.04210323837146</v>
+        <v>36.96604077918407</v>
       </c>
       <c r="I20" t="n">
-        <v>1.192325427442758</v>
+        <v>1.247520118618066</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743205840215633</v>
+        <v>4.744699730751464</v>
       </c>
       <c r="K20" t="n">
-        <v>22.94655598847042</v>
+        <v>22.60060773244793</v>
       </c>
       <c r="L20" t="n">
-        <v>42.95547806236542</v>
+        <v>42.93519304126534</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96027630857273</v>
+        <v>99.95843832568947</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.59865938690388</v>
+        <v>82.93257141607229</v>
       </c>
       <c r="C21" t="n">
-        <v>37.45581232243262</v>
+        <v>37.80792106596117</v>
       </c>
       <c r="D21" t="n">
-        <v>1.22122189351175</v>
+        <v>1.235610087066332</v>
       </c>
       <c r="E21" t="n">
-        <v>13.36964634468141</v>
+        <v>13.55356480507213</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594509033884911</v>
+        <v>0.7597081841087385</v>
       </c>
       <c r="G21" t="n">
-        <v>22.13204440070988</v>
+        <v>22.2867396816427</v>
       </c>
       <c r="H21" t="n">
-        <v>38.61318176114098</v>
+        <v>38.52584296301605</v>
       </c>
       <c r="I21" t="n">
-        <v>1.756545937293307</v>
+        <v>1.822929544486732</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74656814617807</v>
+        <v>4.748176150679615</v>
       </c>
       <c r="K21" t="n">
-        <v>17.40134061309612</v>
+        <v>17.06742858392769</v>
       </c>
       <c r="L21" t="n">
-        <v>45.08433700912327</v>
+        <v>45.0639305211043</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94148994465201</v>
+        <v>99.93928017099317</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_93_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.17383575291625</v>
+        <v>43.60983674562492</v>
       </c>
       <c r="M2" t="n">
-        <v>101.0720056753344</v>
+        <v>95.11260029118063</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01808498016175</v>
+        <v>81.46925251416386</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91639718264624</v>
+        <v>43.2248080697194</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228716270950023</v>
+        <v>2.179975686414086</v>
       </c>
       <c r="E3" t="n">
-        <v>5.698854108738175</v>
+        <v>4.146692329585628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429054236500079</v>
+        <v>0.7376275799422746</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96894982348158</v>
+        <v>32.79046761647854</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17364948790036</v>
+        <v>33.93086867734463</v>
       </c>
       <c r="I3" t="n">
-        <v>6.561850967629052</v>
+        <v>3.073448249759478</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643158897812548</v>
+        <v>4.610172374639216</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98191501983825</v>
+        <v>18.53074748583615</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86614948146661</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7644616839511</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16052588199169</v>
+        <v>88.53821510684617</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69323471859821</v>
+        <v>42.81128074898933</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18767273290922</v>
+        <v>2.185698089958151</v>
       </c>
       <c r="E4" t="n">
-        <v>6.507183366251505</v>
+        <v>6.521115384270794</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444622734458751</v>
+        <v>0.7395638412978335</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34338527654538</v>
+        <v>33.47728240457253</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24526457851024</v>
+        <v>34.01993669970034</v>
       </c>
       <c r="I4" t="n">
-        <v>5.47966844529274</v>
+        <v>6.972344678935057</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652889209036719</v>
+        <v>4.622274008111459</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83947411800831</v>
+        <v>11.46178489315385</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28501752540378</v>
+        <v>45.49513134798995</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8177263620103</v>
+        <v>99.76819699013313</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.95670575231514</v>
+        <v>87.42314313084117</v>
       </c>
       <c r="C5" t="n">
-        <v>42.33994858132162</v>
+        <v>42.77696894950198</v>
       </c>
       <c r="D5" t="n">
-        <v>2.128795550326046</v>
+        <v>2.132647150356729</v>
       </c>
       <c r="E5" t="n">
-        <v>7.094469664575099</v>
+        <v>7.333367149115113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457829134452268</v>
+        <v>0.7412059004543269</v>
       </c>
       <c r="G5" t="n">
-        <v>32.44600947012957</v>
+        <v>32.6647267753096</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30601401848043</v>
+        <v>34.09547142089904</v>
       </c>
       <c r="I5" t="n">
-        <v>4.574490926326088</v>
+        <v>5.823187856866826</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661143209032667</v>
+        <v>4.632536877839543</v>
       </c>
       <c r="K5" t="n">
-        <v>14.04329424768488</v>
+        <v>12.57685686915882</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46454415862425</v>
+        <v>44.45249794025768</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84778698763076</v>
+        <v>99.80632375891848</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.66942546895639</v>
+        <v>86.09636417340046</v>
       </c>
       <c r="C6" t="n">
-        <v>41.76312327710696</v>
+        <v>42.35394410902654</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066131895058216</v>
+        <v>2.0693738210757</v>
       </c>
       <c r="E6" t="n">
-        <v>7.521936326572789</v>
+        <v>7.926092549969746</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469038430796655</v>
+        <v>0.7426010766662301</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49092218993419</v>
+        <v>31.69559973862033</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3575767816646</v>
+        <v>34.15964952664659</v>
       </c>
       <c r="I6" t="n">
-        <v>3.817805413399018</v>
+        <v>4.861790731257909</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668149019247909</v>
+        <v>4.641256729163938</v>
       </c>
       <c r="K6" t="n">
-        <v>15.33057453104361</v>
+        <v>13.90363582659955</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7792329994515</v>
+        <v>43.5806648461276</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87293080760206</v>
+        <v>99.8382447817537</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.31261373372995</v>
+        <v>84.56859114071889</v>
       </c>
       <c r="C7" t="n">
-        <v>40.99933327127939</v>
+        <v>41.58114286632515</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000435323293757</v>
+        <v>1.996730052277431</v>
       </c>
       <c r="E7" t="n">
-        <v>7.813688711078889</v>
+        <v>8.32418195554467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747855802413893</v>
+        <v>0.7437888520757324</v>
       </c>
       <c r="G7" t="n">
-        <v>30.48960875271932</v>
+        <v>30.58295020382631</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40136691103907</v>
+        <v>34.21428719548369</v>
       </c>
       <c r="I7" t="n">
-        <v>3.185559468098194</v>
+        <v>4.057972556037726</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674098765086831</v>
+        <v>4.648680325473328</v>
       </c>
       <c r="K7" t="n">
-        <v>16.68738626627005</v>
+        <v>15.43140885928112</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20723031207836</v>
+        <v>42.85239853185878</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8939498496278</v>
+        <v>99.86495025746505</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.40774132933721</v>
+        <v>82.81065935304905</v>
       </c>
       <c r="C8" t="n">
-        <v>43.3733409289997</v>
+        <v>40.453326575504</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004794319209144</v>
+        <v>1.913520942695597</v>
       </c>
       <c r="E8" t="n">
-        <v>9.70299352019908</v>
+        <v>8.54166643812132</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494853979074645</v>
+        <v>0.7448026737911438</v>
       </c>
       <c r="G8" t="n">
-        <v>31.01057922812044</v>
+        <v>29.30847644512096</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47632830374336</v>
+        <v>34.26092299439262</v>
       </c>
       <c r="I8" t="n">
-        <v>5.77927682323608</v>
+        <v>3.386253147732758</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684283736921652</v>
+        <v>4.655016711194649</v>
       </c>
       <c r="K8" t="n">
-        <v>11.59225867066281</v>
+        <v>17.18934064695095</v>
       </c>
       <c r="L8" t="n">
-        <v>44.84217669955648</v>
+        <v>42.24461131765513</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80777629921897</v>
+        <v>99.88727854011007</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.74018868278242</v>
+        <v>80.84861654823884</v>
       </c>
       <c r="C9" t="n">
-        <v>42.60297715544191</v>
+        <v>39.0167366321039</v>
       </c>
       <c r="D9" t="n">
-        <v>1.930107409926679</v>
+        <v>1.82122171622298</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1456823953349</v>
+        <v>8.600517485878527</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508750891816629</v>
+        <v>0.7456702170217191</v>
       </c>
       <c r="G9" t="n">
-        <v>29.85530644257056</v>
+        <v>27.89477375464254</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54025410235649</v>
+        <v>34.30082998299908</v>
       </c>
       <c r="I9" t="n">
-        <v>4.824993936026722</v>
+        <v>2.825164535088244</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692969307385392</v>
+        <v>4.660438856385745</v>
       </c>
       <c r="K9" t="n">
-        <v>13.2598113172176</v>
+        <v>19.15138345176118</v>
       </c>
       <c r="L9" t="n">
-        <v>43.97667606002841</v>
+        <v>41.73781732869789</v>
       </c>
       <c r="M9" t="n">
-        <v>99.83946453268791</v>
+        <v>99.90593741256296</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.85239135299349</v>
+        <v>85.75191520322014</v>
       </c>
       <c r="C10" t="n">
-        <v>41.46431205389531</v>
+        <v>42.3658089405868</v>
       </c>
       <c r="D10" t="n">
-        <v>1.846127270084362</v>
+        <v>1.823290527620375</v>
       </c>
       <c r="E10" t="n">
-        <v>10.37543585293663</v>
+        <v>10.50750055674094</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520630015617464</v>
+        <v>0.7465172588892364</v>
       </c>
       <c r="G10" t="n">
-        <v>28.5562840165712</v>
+        <v>29.33662591212654</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59489807184033</v>
+        <v>35.74995908102223</v>
       </c>
       <c r="I10" t="n">
-        <v>4.02718938023833</v>
+        <v>2.922288998763075</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700393759760915</v>
+        <v>4.665732868057727</v>
       </c>
       <c r="K10" t="n">
-        <v>15.14760864700648</v>
+        <v>14.24808479677987</v>
       </c>
       <c r="L10" t="n">
-        <v>43.25405168976415</v>
+        <v>43.28880715597236</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86597239066595</v>
+        <v>99.90270089333903</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.66635567501547</v>
+        <v>85.35346307997452</v>
       </c>
       <c r="C11" t="n">
-        <v>39.90320632154231</v>
+        <v>42.32122497416421</v>
       </c>
       <c r="D11" t="n">
-        <v>1.74952682412098</v>
+        <v>1.797915807130864</v>
       </c>
       <c r="E11" t="n">
-        <v>10.39262063745925</v>
+        <v>10.83159413192723</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753082092830609</v>
+        <v>0.7472400817996174</v>
       </c>
       <c r="G11" t="n">
-        <v>27.06204804716714</v>
+        <v>28.98545290879575</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64177627020801</v>
+        <v>35.84167893935033</v>
       </c>
       <c r="I11" t="n">
-        <v>3.360538723038178</v>
+        <v>2.479330699723111</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706763080191306</v>
+        <v>4.670250511247609</v>
       </c>
       <c r="K11" t="n">
-        <v>17.33364432498453</v>
+        <v>14.64653692002548</v>
       </c>
       <c r="L11" t="n">
-        <v>42.65128298179985</v>
+        <v>42.94967369298332</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8881336283267</v>
+        <v>99.91743558717302</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.44808527672264</v>
+        <v>83.2515706976132</v>
       </c>
       <c r="C12" t="n">
-        <v>38.205748692596</v>
+        <v>40.60466203336482</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65245169672129</v>
+        <v>1.708519891707478</v>
       </c>
       <c r="E12" t="n">
-        <v>10.28325415331505</v>
+        <v>10.63766252435773</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539569501714365</v>
+        <v>0.7478587518629412</v>
       </c>
       <c r="G12" t="n">
-        <v>25.56046960569616</v>
+        <v>27.54423909529784</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68201970788607</v>
+        <v>35.8713537042875</v>
       </c>
       <c r="I12" t="n">
-        <v>2.803702224361154</v>
+        <v>2.067819530956345</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712230938571477</v>
+        <v>4.674117199143383</v>
       </c>
       <c r="K12" t="n">
-        <v>19.55191472327736</v>
+        <v>16.74842930238678</v>
       </c>
       <c r="L12" t="n">
-        <v>42.14898828626446</v>
+        <v>42.57803836703386</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90665170213784</v>
+        <v>99.93112970278547</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.18087998913063</v>
+        <v>84.38239679074989</v>
       </c>
       <c r="C13" t="n">
-        <v>36.37233020502873</v>
+        <v>41.55175800641182</v>
       </c>
       <c r="D13" t="n">
-        <v>1.554084362968663</v>
+        <v>1.70981985695593</v>
       </c>
       <c r="E13" t="n">
-        <v>10.06090280404872</v>
+        <v>11.26335336203015</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547087603861784</v>
+        <v>0.7484277767791225</v>
       </c>
       <c r="G13" t="n">
-        <v>24.03890304519325</v>
+        <v>27.86177258719485</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7166029777642</v>
+        <v>36.19522306600032</v>
       </c>
       <c r="I13" t="n">
-        <v>2.338748286356007</v>
+        <v>1.926126536920029</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716929752413614</v>
+        <v>4.677673604869517</v>
       </c>
       <c r="K13" t="n">
-        <v>21.81912001086939</v>
+        <v>15.61760320925009</v>
       </c>
       <c r="L13" t="n">
-        <v>41.73066916675851</v>
+        <v>42.76648338050249</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92211938265662</v>
+        <v>99.9358445961644</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.4668172758381</v>
+        <v>82.35093498869128</v>
       </c>
       <c r="C14" t="n">
-        <v>40.21437547391154</v>
+        <v>39.81942935547364</v>
       </c>
       <c r="D14" t="n">
-        <v>1.555969142733141</v>
+        <v>1.625815827547486</v>
       </c>
       <c r="E14" t="n">
-        <v>12.23440215615978</v>
+        <v>10.97767248581293</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556240644929215</v>
+        <v>0.7489143474533244</v>
       </c>
       <c r="G14" t="n">
-        <v>25.71715174927353</v>
+        <v>26.4929142514676</v>
       </c>
       <c r="H14" t="n">
-        <v>36.40780150184372</v>
+        <v>36.21875444021775</v>
       </c>
       <c r="I14" t="n">
-        <v>3.073218258254244</v>
+        <v>1.606148964608901</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722650403080759</v>
+        <v>4.680714671583279</v>
       </c>
       <c r="K14" t="n">
-        <v>15.53318272416191</v>
+        <v>17.64906501130872</v>
       </c>
       <c r="L14" t="n">
-        <v>44.15012528188827</v>
+        <v>42.47800211830319</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89768347996171</v>
+        <v>99.94649648508556</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.82871072050881</v>
+        <v>81.43009491201593</v>
       </c>
       <c r="C15" t="n">
-        <v>40.05187642653205</v>
+        <v>39.11981570826095</v>
       </c>
       <c r="D15" t="n">
-        <v>1.532398397421157</v>
+        <v>1.587070378153488</v>
       </c>
       <c r="E15" t="n">
-        <v>12.47633914285089</v>
+        <v>10.94373656280409</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563943405308684</v>
+        <v>0.7493331379922473</v>
       </c>
       <c r="G15" t="n">
-        <v>25.32757305045241</v>
+        <v>25.86155130676174</v>
       </c>
       <c r="H15" t="n">
-        <v>36.44491527099031</v>
+        <v>36.23900785336534</v>
       </c>
       <c r="I15" t="n">
-        <v>2.563625889945236</v>
+        <v>1.366063560487481</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727464628317927</v>
+        <v>4.683332112451547</v>
       </c>
       <c r="K15" t="n">
-        <v>16.17128927949121</v>
+        <v>18.56990508798406</v>
       </c>
       <c r="L15" t="n">
-        <v>43.69146712013634</v>
+        <v>42.26476920078873</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9146328261596</v>
+        <v>99.95448999703375</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.47403793925804</v>
+        <v>78.97504824548298</v>
       </c>
       <c r="C16" t="n">
-        <v>38.09409130138584</v>
+        <v>36.87637576924632</v>
       </c>
       <c r="D16" t="n">
-        <v>1.441929289979149</v>
+        <v>1.486297348163877</v>
       </c>
       <c r="E16" t="n">
-        <v>12.09613678956673</v>
+        <v>10.43867250048294</v>
       </c>
       <c r="F16" t="n">
-        <v>0.757056040228219</v>
+        <v>0.7496933533015397</v>
       </c>
       <c r="G16" t="n">
-        <v>23.83229419124533</v>
+        <v>24.21943957606057</v>
       </c>
       <c r="H16" t="n">
-        <v>36.47679756850705</v>
+        <v>36.2564284701251</v>
       </c>
       <c r="I16" t="n">
-        <v>2.138223808305187</v>
+        <v>1.138933539214321</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731600251426369</v>
+        <v>4.685583458134625</v>
       </c>
       <c r="K16" t="n">
-        <v>18.52596206074197</v>
+        <v>21.02495175451701</v>
       </c>
       <c r="L16" t="n">
-        <v>43.30873480759593</v>
+        <v>42.06072626622312</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92878816972375</v>
+        <v>99.96205378998644</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.07708467813741</v>
+        <v>83.90150731277868</v>
       </c>
       <c r="C17" t="n">
-        <v>39.2600800294982</v>
+        <v>40.11368303895704</v>
       </c>
       <c r="D17" t="n">
-        <v>1.443174110777974</v>
+        <v>1.487066021654487</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8527017715588</v>
+        <v>12.16317285046429</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577096084103079</v>
+        <v>0.7500810747810146</v>
       </c>
       <c r="G17" t="n">
-        <v>24.24038785413343</v>
+        <v>25.73410882291715</v>
       </c>
       <c r="H17" t="n">
-        <v>36.89580725959723</v>
+        <v>37.7773229277587</v>
       </c>
       <c r="I17" t="n">
-        <v>2.151619021095261</v>
+        <v>1.301748897821701</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735685052564424</v>
+        <v>4.688006717381343</v>
       </c>
       <c r="K17" t="n">
-        <v>16.92291532186256</v>
+        <v>16.09849268722131</v>
       </c>
       <c r="L17" t="n">
-        <v>43.74534587778077</v>
+        <v>43.74445507329224</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92834122914154</v>
+        <v>99.9566307994706</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.77398310379077</v>
+        <v>85.49696514190425</v>
       </c>
       <c r="C18" t="n">
-        <v>37.28970774568594</v>
+        <v>40.84306885795148</v>
       </c>
       <c r="D18" t="n">
-        <v>1.357928266248554</v>
+        <v>1.488294977835638</v>
       </c>
       <c r="E18" t="n">
-        <v>12.39257175595632</v>
+        <v>12.76380413107164</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582706765868665</v>
+        <v>0.750700964389003</v>
       </c>
       <c r="G18" t="n">
-        <v>22.80854929847061</v>
+        <v>25.87402272778833</v>
       </c>
       <c r="H18" t="n">
-        <v>36.92312783607142</v>
+        <v>37.80854324605212</v>
       </c>
       <c r="I18" t="n">
-        <v>1.794343541789072</v>
+        <v>2.119718067336255</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739191728667915</v>
+        <v>4.691881027431271</v>
       </c>
       <c r="K18" t="n">
-        <v>19.22601689620924</v>
+        <v>14.50303485809573</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42450816307438</v>
+        <v>44.58329736012011</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94023280496957</v>
+        <v>99.92940107616732</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.84656531749695</v>
+        <v>82.74284867222661</v>
       </c>
       <c r="C19" t="n">
-        <v>36.63911659177258</v>
+        <v>38.41711161853698</v>
       </c>
       <c r="D19" t="n">
-        <v>1.324307470957961</v>
+        <v>1.387130726111391</v>
       </c>
       <c r="E19" t="n">
-        <v>12.33511549259036</v>
+        <v>12.19082177755031</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587443099677023</v>
+        <v>0.7512355549253434</v>
       </c>
       <c r="G19" t="n">
-        <v>22.24383495685241</v>
+        <v>24.11528122335925</v>
       </c>
       <c r="H19" t="n">
-        <v>36.94619087465119</v>
+        <v>37.835467534645</v>
       </c>
       <c r="I19" t="n">
-        <v>1.496220275179209</v>
+        <v>1.767689637351907</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742151937298138</v>
+        <v>4.695222218283399</v>
       </c>
       <c r="K19" t="n">
-        <v>20.15343468250303</v>
+        <v>17.25715132777339</v>
       </c>
       <c r="L19" t="n">
-        <v>43.15760584956357</v>
+        <v>44.26685599626361</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95015712383919</v>
+        <v>99.94111894257398</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.39939226755206</v>
+        <v>79.90433135241484</v>
       </c>
       <c r="C20" t="n">
-        <v>34.4226375519762</v>
+        <v>35.85146441176674</v>
       </c>
       <c r="D20" t="n">
-        <v>1.23470542401387</v>
+        <v>1.283460510356021</v>
       </c>
       <c r="E20" t="n">
-        <v>11.70844715454585</v>
+        <v>11.52537775192834</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591519569202345</v>
+        <v>0.7516974850555749</v>
       </c>
       <c r="G20" t="n">
-        <v>20.7388271035185</v>
+        <v>22.31297350977011</v>
       </c>
       <c r="H20" t="n">
-        <v>36.96604077918407</v>
+        <v>37.85873233132703</v>
       </c>
       <c r="I20" t="n">
-        <v>1.247520118618066</v>
+        <v>1.473980482380435</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744699730751464</v>
+        <v>4.698109281597345</v>
       </c>
       <c r="K20" t="n">
-        <v>22.60060773244793</v>
+        <v>20.09566864758515</v>
       </c>
       <c r="L20" t="n">
-        <v>42.93519304126534</v>
+        <v>44.00376445072165</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95843832568947</v>
+        <v>99.95089751007355</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.93257141607229</v>
+        <v>76.99601177083113</v>
       </c>
       <c r="C21" t="n">
-        <v>37.80792106596117</v>
+        <v>33.16990918696806</v>
       </c>
       <c r="D21" t="n">
-        <v>1.235610087066332</v>
+        <v>1.177807763589127</v>
       </c>
       <c r="E21" t="n">
-        <v>13.55356480507213</v>
+        <v>10.78145255516738</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597081841087385</v>
+        <v>0.7520974252964318</v>
       </c>
       <c r="G21" t="n">
-        <v>22.2867396816427</v>
+        <v>20.47619947517966</v>
       </c>
       <c r="H21" t="n">
-        <v>38.52584296301605</v>
+        <v>37.87887504941262</v>
       </c>
       <c r="I21" t="n">
-        <v>1.822929544486732</v>
+        <v>1.228970594083201</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748176150679615</v>
+        <v>4.7006089081027</v>
       </c>
       <c r="K21" t="n">
-        <v>17.06742858392769</v>
+        <v>23.00398822916886</v>
       </c>
       <c r="L21" t="n">
-        <v>45.0639305211043</v>
+        <v>43.78515868157474</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93928017099317</v>
+        <v>99.95905609771165</v>
       </c>
     </row>
   </sheetData>
